--- a/outputs/46240.xlsx
+++ b/outputs/46240.xlsx
@@ -186,32 +186,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -407,164 +411,164 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="3" customFormat="true" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>44613</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>44562</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <v>44562</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <v>44563</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="6" t="str">
-        <f aca="false">IF(H2="N/A","N/A",IF(H2="Yes","Yes",IF(ISNUMBER(H2),"Yes","No")))</f>
+      <c r="J2" s="7" t="str">
+        <f aca="false">IF(H2="","No",IF(H2="N/A","N/A","Yes"))</f>
         <v>Yes</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>44620</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>44566</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>44568</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="6" t="str">
-        <f aca="false">IF(H3="N/A","N/A",IF(H3="Yes","Yes",IF(ISNUMBER(H3),"Yes","No")))</f>
+      <c r="J3" s="7" t="str">
+        <f aca="false">IF(H3="","No",IF(H3="N/A","N/A","Yes"))</f>
         <v>Yes</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>44620</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="4"/>
+      <c r="F4" s="6" t="n">
         <v>44566</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>44567</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="6" t="str">
-        <f aca="false">IF(H4="N/A","N/A",IF(H4="Yes","Yes",IF(ISNUMBER(H4),"Yes","No")))</f>
+      <c r="J4" s="7" t="str">
+        <f aca="false">IF(H4="","No",IF(H4="N/A","N/A","Yes"))</f>
         <v>N/A</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/46240.xlsx
+++ b/outputs/46240.xlsx
@@ -463,7 +463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -492,7 +492,7 @@
         <v>16</v>
       </c>
       <c r="J2" s="7" t="str">
-        <f aca="false">IF(H2="","No",IF(H2="N/A","N/A","Yes"))</f>
+        <f aca="false">IF(ISNUMBER(H2),"Yes",IF(H2="N/A","N/A",IF(H2="Yes","Yes","No")))</f>
         <v>Yes</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -502,7 +502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -531,13 +531,13 @@
         <v>16</v>
       </c>
       <c r="J3" s="7" t="str">
-        <f aca="false">IF(H3="","No",IF(H3="N/A","N/A","Yes"))</f>
+        <f aca="false">IF(ISNUMBER(H3),"Yes",IF(H3="N/A","N/A",IF(H3="Yes","Yes","No")))</f>
         <v>Yes</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
@@ -564,7 +564,7 @@
         <v>16</v>
       </c>
       <c r="J4" s="7" t="str">
-        <f aca="false">IF(H4="","No",IF(H4="N/A","N/A","Yes"))</f>
+        <f aca="false">IF(ISNUMBER(H4),"Yes",IF(H4="N/A","N/A",IF(H4="Yes","Yes","No")))</f>
         <v>N/A</v>
       </c>
       <c r="K4" s="7"/>
